--- a/data/trending_integrated_20261021_15.xlsx
+++ b/data/trending_integrated_20261021_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2415</v>
+        <v>2410</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+25.52%</t>
+          <t>'+25.26%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>3.15</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="H2" t="n">
         <v>3.94</v>
@@ -610,7 +610,7 @@
         <v>0.79</v>
       </c>
       <c r="O2" t="n">
-        <v>13856660964</v>
+        <v>14589361924</v>
       </c>
       <c r="P2" t="n">
         <v>2665</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14790</v>
+        <v>14840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.43%</t>
+          <t>'+22.85%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0.27</v>
       </c>
       <c r="O3" t="n">
-        <v>103799754150</v>
+        <v>105023694775</v>
       </c>
       <c r="P3" t="n">
         <v>28800</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10170</v>
+        <v>10190</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.57%</t>
+          <t>'+17.80%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.66</v>
       </c>
       <c r="E4" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F4" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G4" t="n">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="H4" t="n">
         <v>5.34</v>
@@ -794,7 +794,7 @@
         <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>62440402425</v>
+        <v>65167125240</v>
       </c>
       <c r="P4" t="n">
         <v>14940</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11060</v>
+        <v>11140</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.20%</t>
+          <t>'+14.02%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F5" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G5" t="n">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="H5" t="n">
         <v>1.28</v>
@@ -886,7 +886,7 @@
         <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>297526893620</v>
+        <v>300978069265</v>
       </c>
       <c r="P5" t="n">
         <v>11690</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14310</v>
+        <v>14320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.24%</t>
+          <t>'+12.31%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>583</v>
+        <v>639</v>
       </c>
       <c r="H6" t="n">
         <v>3.15</v>
@@ -969,7 +969,7 @@
         <v>13080</v>
       </c>
       <c r="L6" t="n">
-        <v>14330</v>
+        <v>14350</v>
       </c>
       <c r="M6" t="n">
         <v>12680</v>
@@ -978,7 +978,7 @@
         <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>136726905275</v>
+        <v>143546497840</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1296000</v>
+        <v>1300000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.97%</t>
+          <t>'+6.30%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="G7" t="n">
-        <v>1555</v>
+        <v>1517</v>
       </c>
       <c r="H7" t="n">
         <v>48.77</v>
@@ -1070,7 +1070,7 @@
         <v>48.81</v>
       </c>
       <c r="O7" t="n">
-        <v>4535829093500</v>
+        <v>4660121648500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>자사주 매입 완료 후 주가 하락에 대한 불만 표출. 정치적 이슈와 함께 메모리 반도체 호재 및 주주 친화책 기대.</t>
+          <t>자사주 매입 종료 이후 주주 친화책에 대한 기대감에도 불구하고, 정치적 이슈와 부정적인 시장 전망, 그리고 주가 하락에 대한 불만이 표출되고 있다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['메모리', '자사주 매입', '주가 전망']</t>
+          <t>['자사주 매입', '주주 친화책', '반도체']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G8" t="n">
-        <v>1662</v>
+        <v>1619</v>
       </c>
       <c r="H8" t="n">
         <v>46.08</v>
@@ -1162,7 +1162,7 @@
         <v>46.04</v>
       </c>
       <c r="O8" t="n">
-        <v>3066701138750</v>
+        <v>3151848558500</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 언급과 함께 주가 상승 및 하락에 대한 상반된 기대가 혼재. 공매도 관련 언급 존재.</t>
+          <t>미국 정부의 중국 반도체 퇴출 결정 및 마이크론 대만 공장 파업 소식이 호재로 작용할 수 있다는 기대감이 있으나, 정치적 언급과 부정적인 시장 전망이 혼재되어 있다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '주가 전망', '공매도']</t>
+          <t>['반도체', '미국 정부', '퇴출 결정']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1579</v>
+        <v>1593</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.88%</t>
+          <t>'+4.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.12</v>
       </c>
       <c r="E9" t="n">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="F9" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G9" t="n">
-        <v>498</v>
+        <v>531</v>
       </c>
       <c r="H9" t="n">
         <v>0.6899999999999999</v>
@@ -1254,7 +1254,7 @@
         <v>0.57</v>
       </c>
       <c r="O9" t="n">
-        <v>79873001418</v>
+        <v>80946075794</v>
       </c>
       <c r="P9" t="n">
         <v>3980</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주당 3500원 인수 관련 언급과 함께 주가 급등락 및 상장폐지 우려 제기. 거래량에 기반한 움직임 분석.</t>
+          <t>주당 3500원 인수설에 대한 엇갈린 반응과 함께, 상장폐지 가능성 및 단기 급등락에 대한 언급이 혼재되어 있다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['인수', '상폐', '거래량']</t>
+          <t>['인수설', '상장폐지', '급등락']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14700</v>
+        <v>14730</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.81%</t>
+          <t>'+4.03%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F10" t="n">
         <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H10" t="n">
         <v>9.82</v>
@@ -1346,7 +1346,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>30972931985</v>
+        <v>31453460875</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2910</v>
+        <v>2905</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.46%</t>
+          <t>'+2.29%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
         <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="H11" t="n">
         <v>5.82</v>
@@ -1438,7 +1438,7 @@
         <v>5.91</v>
       </c>
       <c r="O11" t="n">
-        <v>17477624736</v>
+        <v>17548834366</v>
       </c>
       <c r="P11" t="n">
         <v>19950</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17660</v>
+        <v>17670</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.96%</t>
+          <t>'+2.02%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.78</v>
       </c>
       <c r="O12" t="n">
-        <v>43730965160</v>
+        <v>44563506595</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7340</v>
+        <v>7350</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.96%</t>
+          <t>'+1.10%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H13" t="n">
         <v>25.45</v>
@@ -1622,7 +1622,7 @@
         <v>25.4</v>
       </c>
       <c r="O13" t="n">
-        <v>14636992720</v>
+        <v>15070654680</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1682,13 +1682,13 @@
         <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F14" t="n">
         <v>102</v>
       </c>
       <c r="G14" t="n">
-        <v>608</v>
+        <v>653</v>
       </c>
       <c r="H14" t="n">
         <v>22.23</v>
@@ -1714,7 +1714,7 @@
         <v>22.29</v>
       </c>
       <c r="O14" t="n">
-        <v>88304325500</v>
+        <v>89539508450</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>원전 및 전력 섹터 상승 기대에도 불구하고 주가 하락에 대한 불만. 외국인 및 연기금 매매 동향 언급.</t>
+          <t>반도체 섹터의 상승 기대감 속에서 원전 및 전력 섹터의 상승 가능성이 언급되었으나, 주가 하락 및 정부 정책에 대한 불만이 제기되고 있다.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '전력', '외국인 매매']</t>
+          <t>['원전', '전력', '주가 하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.65%</t>
+          <t>'-1.84%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.93</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H15" t="n">
         <v>0.84</v>
@@ -1800,13 +1800,13 @@
         <v>1715</v>
       </c>
       <c r="M15" t="n">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="N15" t="n">
         <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>32699881699</v>
+        <v>33061784854</v>
       </c>
       <c r="P15" t="n">
         <v>2970</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3100</v>
+        <v>3080</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.17%</t>
+          <t>'-4.79%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.73</v>
       </c>
       <c r="E16" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F16" t="n">
         <v>46</v>
       </c>
       <c r="G16" t="n">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>11471208201</v>
+        <v>11648320333</v>
       </c>
       <c r="P16" t="n">
         <v>7050</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4275</v>
+        <v>4310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.67%</t>
+          <t>'-6.91%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F17" t="n">
         <v>73</v>
       </c>
       <c r="G17" t="n">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="H17" t="n">
         <v>8.58</v>
@@ -1990,7 +1990,7 @@
         <v>8.57</v>
       </c>
       <c r="O17" t="n">
-        <v>25413545141</v>
+        <v>25832839791</v>
       </c>
       <c r="P17" t="n">
         <v>7560</v>

--- a/data/trending_integrated_20261021_15.xlsx
+++ b/data/trending_integrated_20261021_15.xlsx
@@ -563,70 +563,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>형지엘리트</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2410</v>
+        <v>14990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+25.26%</t>
+          <t>'+24.09%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.15</v>
+        <v>-0.27</v>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>236</v>
+        <v>151</v>
       </c>
       <c r="H2" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1924</v>
+        <v>12080</v>
       </c>
       <c r="K2" t="n">
-        <v>2310</v>
+        <v>12280</v>
       </c>
       <c r="L2" t="n">
-        <v>2500</v>
+        <v>15640</v>
       </c>
       <c r="M2" t="n">
-        <v>2155</v>
+        <v>12280</v>
       </c>
       <c r="N2" t="n">
-        <v>0.79</v>
+        <v>0.27</v>
       </c>
       <c r="O2" t="n">
-        <v>14589361924</v>
+        <v>108149774120</v>
       </c>
       <c r="P2" t="n">
-        <v>2665</v>
+        <v>28800</v>
       </c>
       <c r="Q2" t="n">
-        <v>292</v>
+        <v>12030</v>
       </c>
       <c r="R2" t="n">
-        <v>-105000</v>
+        <v>135000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>역대 최대 매출 및 3년 새 2배 성장 전망. 퀀텀 점프 기대감으로 상한가 및 연상 기대.</t>
+          <t>엘리스 후속주로 부각되며 급등. 노광 장비 관련주.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['역대 최대 매출', '퀀텀 점프', '성장 전망']</t>
+          <t>['노광 장비', '엘리스', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,86 +648,86 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>093240</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14840</v>
+        <v>10190</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.85%</t>
+          <t>'+17.80%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.27</v>
+        <v>-0.66</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>218</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="G3" t="n">
-        <v>140</v>
+        <v>583</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>12080</v>
+        <v>8650</v>
       </c>
       <c r="K3" t="n">
-        <v>12280</v>
+        <v>9010</v>
       </c>
       <c r="L3" t="n">
-        <v>15640</v>
+        <v>10460</v>
       </c>
       <c r="M3" t="n">
-        <v>12280</v>
+        <v>8790</v>
       </c>
       <c r="N3" t="n">
-        <v>0.27</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>105023694775</v>
+        <v>66596841720</v>
       </c>
       <c r="P3" t="n">
-        <v>28800</v>
+        <v>14940</v>
       </c>
       <c r="Q3" t="n">
-        <v>12030</v>
+        <v>5390</v>
       </c>
       <c r="R3" t="n">
-        <v>135000</v>
+        <v>370000</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>엘리스 후속주로 부각되며 급등. 노광 장비 관련주.</t>
+          <t>미국 중복 상장 시도 실패 소식과 함께 1만원대 안착 전망이 제시되었으며, 테슬라 관련 호재 및 주가 관리 기대감이 나타났습니다.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['노광 장비', '엘리스', '급등']</t>
+          <t>['중복상장', '주가관리', '전망']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>형지엘리트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10190</v>
+        <v>2220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.80%</t>
+          <t>'+15.38%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.66</v>
+        <v>3.15</v>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>588</v>
+        <v>241</v>
       </c>
       <c r="H4" t="n">
-        <v>5.34</v>
+        <v>3.94</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,60 +779,60 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8650</v>
+        <v>1924</v>
       </c>
       <c r="K4" t="n">
-        <v>9010</v>
+        <v>2310</v>
       </c>
       <c r="L4" t="n">
-        <v>10460</v>
+        <v>2500</v>
       </c>
       <c r="M4" t="n">
-        <v>8790</v>
+        <v>2090</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>0.79</v>
       </c>
       <c r="O4" t="n">
-        <v>65167125240</v>
+        <v>15687082363</v>
       </c>
       <c r="P4" t="n">
-        <v>14940</v>
+        <v>2665</v>
       </c>
       <c r="Q4" t="n">
-        <v>5390</v>
+        <v>292</v>
       </c>
       <c r="R4" t="n">
-        <v>370000</v>
+        <v>-105000</v>
       </c>
       <c r="S4" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>국내 주가 관리 포기 및 미국 중복 상장 시도 실패 언급. 테슬라 관련 기대감과 함께 주가 상승 및 1만원대 안착 전망.</t>
+          <t>역대 최대 매출 및 3년 새 2배 성장 전망. 퀀텀 점프 기대감으로 상한가 및 연상 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['중복상장', '테슬라', '주가 전망']</t>
+          <t>['역대 최대 매출', '퀀텀 점프', '성장 전망']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>093240</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11140</v>
+        <v>11110</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.02%</t>
+          <t>'+13.72%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F5" t="n">
         <v>146</v>
       </c>
       <c r="G5" t="n">
-        <v>581</v>
+        <v>613</v>
       </c>
       <c r="H5" t="n">
         <v>1.28</v>
@@ -886,7 +886,7 @@
         <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>300978069265</v>
+        <v>306035986030</v>
       </c>
       <c r="P5" t="n">
         <v>11690</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 수주 잔고 1조 돌파 기반 신고가 경신 및 목표가 상향 제시. 로봇 및 AI 섹터 강세에 따른 기대감.</t>
+          <t>인공지능 데이터센터 수주 잔고 1조원 돌파 및 삼성 관련 호재를 바탕으로 신고가 재돌파 기대감이 높으며, 9일 연속 상승세를 보이고 있습니다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['인공지능', '수주잔고', '신고가']</t>
+          <t>['수주잔고', '로봇주', '신고가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14320</v>
+        <v>14280</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.31%</t>
+          <t>'+12.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G6" t="n">
-        <v>639</v>
+        <v>699</v>
       </c>
       <c r="H6" t="n">
         <v>3.15</v>
@@ -969,7 +969,7 @@
         <v>13080</v>
       </c>
       <c r="L6" t="n">
-        <v>14350</v>
+        <v>14380</v>
       </c>
       <c r="M6" t="n">
         <v>12680</v>
@@ -978,7 +978,7 @@
         <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>143546497840</v>
+        <v>148117281305</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1300000</v>
+        <v>1296000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.30%</t>
+          <t>'+5.97%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="G7" t="n">
-        <v>1517</v>
+        <v>1576</v>
       </c>
       <c r="H7" t="n">
         <v>48.77</v>
@@ -1070,7 +1070,7 @@
         <v>48.81</v>
       </c>
       <c r="O7" t="n">
-        <v>4660121648500</v>
+        <v>4754942329000</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>자사주 매입 종료 이후 주주 친화책에 대한 기대감에도 불구하고, 정치적 이슈와 부정적인 시장 전망, 그리고 주가 하락에 대한 불만이 표출되고 있다.</t>
+          <t>자사주 매입 완료 및 솔리다임 상장 관련 언급이 있으나, 전반적으로 이재명 정부와 최태원 회장에 대한 부정적 평가와 함께 주가 하락에 대한 불만이 표출되었습니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['자사주 매입', '주주 친화책', '반도체']</t>
+          <t>['솔리다임', '자사주', '주가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>222500</v>
+        <v>1601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.20%</t>
+          <t>'+5.33%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>290</v>
       </c>
       <c r="F8" t="n">
-        <v>521</v>
+        <v>133</v>
       </c>
       <c r="G8" t="n">
-        <v>1619</v>
+        <v>543</v>
       </c>
       <c r="H8" t="n">
-        <v>46.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>211500</v>
+        <v>1520</v>
       </c>
       <c r="K8" t="n">
-        <v>217000</v>
+        <v>1132</v>
       </c>
       <c r="L8" t="n">
-        <v>228000</v>
+        <v>1952</v>
       </c>
       <c r="M8" t="n">
-        <v>217000</v>
+        <v>1115</v>
       </c>
       <c r="N8" t="n">
-        <v>46.04</v>
+        <v>0.57</v>
       </c>
       <c r="O8" t="n">
-        <v>3151848558500</v>
+        <v>82907724731</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>3980</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>1115</v>
       </c>
       <c r="R8" t="n">
-        <v>1750000</v>
+        <v>-184000</v>
       </c>
       <c r="S8" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 정부의 중국 반도체 퇴출 결정 및 마이크론 대만 공장 파업 소식이 호재로 작용할 수 있다는 기대감이 있으나, 정치적 언급과 부정적인 시장 전망이 혼재되어 있다.</t>
+          <t>주당 3500원 인수 관련 언급과 함께 3연상 및 60% 상승에 대한 기대감이 있었으나, 상폐 및 거래정지 가능성도 제기되었습니다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '미국 정부', '퇴출 결정']</t>
+          <t>['인수', '공시', '상폐']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>290720</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1593</v>
+        <v>222500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.80%</t>
+          <t>'+5.20%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>291</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>130</v>
+        <v>522</v>
       </c>
       <c r="G9" t="n">
-        <v>531</v>
+        <v>1611</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6899999999999999</v>
+        <v>46.08</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1520</v>
+        <v>211500</v>
       </c>
       <c r="K9" t="n">
-        <v>1132</v>
+        <v>217000</v>
       </c>
       <c r="L9" t="n">
-        <v>1952</v>
+        <v>228000</v>
       </c>
       <c r="M9" t="n">
-        <v>1115</v>
+        <v>217000</v>
       </c>
       <c r="N9" t="n">
-        <v>0.57</v>
+        <v>46.04</v>
       </c>
       <c r="O9" t="n">
-        <v>80946075794</v>
+        <v>3204583304750</v>
       </c>
       <c r="P9" t="n">
-        <v>3980</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>1115</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-184000</v>
+        <v>1750000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주당 3500원 인수설에 대한 엇갈린 반응과 함께, 상장폐지 가능성 및 단기 급등락에 대한 언급이 혼재되어 있다.</t>
+          <t>미국 정부의 중국 반도체 퇴출 결정과 나스닥 선물 폭락 등 부정적 요인이 언급되었으나, 25만원 및 30만원 돌파 기대와 함께 100만원 황제주 가능성도 제기되었습니다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['인수설', '상장폐지', '급등락']</t>
+          <t>['반도체', '퇴출', '전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14730</v>
+        <v>14710</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.03%</t>
+          <t>'+3.88%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H10" t="n">
         <v>9.82</v>
@@ -1346,7 +1346,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>31453460875</v>
+        <v>31985349175</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2905</v>
+        <v>2915</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.29%</t>
+          <t>'+2.64%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H11" t="n">
         <v>5.82</v>
@@ -1438,7 +1438,7 @@
         <v>5.91</v>
       </c>
       <c r="O11" t="n">
-        <v>17548834366</v>
+        <v>17732637409</v>
       </c>
       <c r="P11" t="n">
         <v>19950</v>
@@ -1498,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12" t="n">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.78</v>
       </c>
       <c r="O12" t="n">
-        <v>44563506595</v>
+        <v>45304104130</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7350</v>
+        <v>63500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.10%</t>
+          <t>'+1.11%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>91</v>
+        <v>187</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="G13" t="n">
-        <v>416</v>
+        <v>660</v>
       </c>
       <c r="H13" t="n">
-        <v>25.45</v>
+        <v>22.23</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7270</v>
+        <v>62800</v>
       </c>
       <c r="K13" t="n">
-        <v>7360</v>
+        <v>63600</v>
       </c>
       <c r="L13" t="n">
-        <v>7520</v>
+        <v>64800</v>
       </c>
       <c r="M13" t="n">
-        <v>7250</v>
+        <v>62600</v>
       </c>
       <c r="N13" t="n">
-        <v>25.4</v>
+        <v>22.29</v>
       </c>
       <c r="O13" t="n">
-        <v>15070654680</v>
+        <v>90956372350</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>7190</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>272000</v>
+        <v>-13000</v>
       </c>
       <c r="S13" t="n">
-        <v>-15000</v>
+        <v>19000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 매도세 및 개인 투자자들의 신용 문제, 그리고 실적 발표에 대한 불확실성이 혼재된 가운데, 부정적인 전망이 우세합니다.</t>
+          <t>야간 선물 폭등과 반도체 및 원전/전력 섹터 상승 기대감이 있으나, 주가 누르기 및 하락에 대한 불만과 함께 외인 매도에 따른 박살 가능성이 언급되었습니다.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외인매도', '실적발표', '신용']</t>
+          <t>['원전', '전력', '주가']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63400</v>
+        <v>7350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.96%</t>
+          <t>'+1.10%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>182</v>
+        <v>93</v>
       </c>
       <c r="F14" t="n">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>653</v>
+        <v>418</v>
       </c>
       <c r="H14" t="n">
-        <v>22.23</v>
+        <v>25.45</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62800</v>
+        <v>7270</v>
       </c>
       <c r="K14" t="n">
-        <v>63600</v>
+        <v>7360</v>
       </c>
       <c r="L14" t="n">
-        <v>64800</v>
+        <v>7520</v>
       </c>
       <c r="M14" t="n">
-        <v>62600</v>
+        <v>7250</v>
       </c>
       <c r="N14" t="n">
-        <v>22.29</v>
+        <v>25.4</v>
       </c>
       <c r="O14" t="n">
-        <v>89539508450</v>
+        <v>15825518915</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>7190</v>
       </c>
       <c r="R14" t="n">
-        <v>-13000</v>
+        <v>272000</v>
       </c>
       <c r="S14" t="n">
-        <v>19000</v>
+        <v>-15000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 섹터의 상승 기대감 속에서 원전 및 전력 섹터의 상승 가능성이 언급되었으나, 주가 하락 및 정부 정책에 대한 불만이 제기되고 있다.</t>
+          <t>외국인 매도세 및 개인 투자자들의 신용 문제, 그리고 실적 발표에 대한 불확실성이 혼재된 가운데, 부정적인 전망이 우세합니다.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '전력', '주가 하락']</t>
+          <t>['외인매도', '실적발표', '신용']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1544</v>
+        <v>1550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.84%</t>
+          <t>'-1.46%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>102</v>
       </c>
       <c r="F15" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H15" t="n">
         <v>0.84</v>
@@ -1806,7 +1806,7 @@
         <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>33061784854</v>
+        <v>33210054941</v>
       </c>
       <c r="P15" t="n">
         <v>2970</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3080</v>
+        <v>3090</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.79%</t>
+          <t>'-4.48%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1898,7 +1898,7 @@
         <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>11648320333</v>
+        <v>11980563325</v>
       </c>
       <c r="P16" t="n">
         <v>7050</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4310</v>
+        <v>4305</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.91%</t>
+          <t>'-7.02%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F17" t="n">
         <v>73</v>
       </c>
       <c r="G17" t="n">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="H17" t="n">
         <v>8.58</v>
@@ -1990,7 +1990,7 @@
         <v>8.57</v>
       </c>
       <c r="O17" t="n">
-        <v>25832839791</v>
+        <v>26089269291</v>
       </c>
       <c r="P17" t="n">
         <v>7560</v>

--- a/data/trending_integrated_20261021_15.xlsx
+++ b/data/trending_integrated_20261021_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14990</v>
+        <v>14980</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.09%</t>
+          <t>'+24.01%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.27</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0.27</v>
       </c>
       <c r="O2" t="n">
-        <v>108149774120</v>
+        <v>108874132020</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.66</v>
       </c>
       <c r="E3" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F3" t="n">
         <v>114</v>
       </c>
       <c r="G3" t="n">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="H3" t="n">
         <v>5.34</v>
@@ -702,7 +702,7 @@
         <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>66596841720</v>
+        <v>67986492780</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 중복 상장 시도 실패 소식과 함께 1만원대 안착 전망이 제시되었으며, 테슬라 관련 호재 및 주가 관리 기대감이 나타났습니다.</t>
+          <t>미국 증시 상장 관련 이슈와 함께 주가 변동성 확대. 테슬라 관련 뉴스가 긍정적 영향을 미치나, 국내 주가 관리 및 거래량에 대한 불만이 제기됨.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['중복상장', '주가관리', '전망']</t>
+          <t>['중복상장', '테슬라', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,123 +747,123 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>형지엘리트</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2220</v>
+        <v>11140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.38%</t>
+          <t>'+14.02%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.15</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>249</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>151</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>640</v>
       </c>
       <c r="H4" t="n">
-        <v>3.94</v>
+        <v>1.28</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1924</v>
+        <v>9770</v>
       </c>
       <c r="K4" t="n">
-        <v>2310</v>
+        <v>10320</v>
       </c>
       <c r="L4" t="n">
-        <v>2500</v>
+        <v>11690</v>
       </c>
       <c r="M4" t="n">
-        <v>2090</v>
+        <v>9690</v>
       </c>
       <c r="N4" t="n">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="O4" t="n">
-        <v>15687082363</v>
+        <v>307443591870</v>
       </c>
       <c r="P4" t="n">
-        <v>2665</v>
+        <v>11690</v>
       </c>
       <c r="Q4" t="n">
-        <v>292</v>
+        <v>2270</v>
       </c>
       <c r="R4" t="n">
-        <v>-105000</v>
+        <v>-83000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-114000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>역대 최대 매출 및 3년 새 2배 성장 전망. 퀀텀 점프 기대감으로 상한가 및 연상 기대.</t>
+          <t>데이터센터 수주 잔고 1조 원 이상 확보 소식과 함께 로봇 및 AI 섹터 전반의 강세. 삼성전자와의 연계 가능성이 부각되며 신고가 경신 기대감이 높음.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['역대 최대 매출', '퀀텀 점프', '성장 전망']</t>
+          <t>['데이터센터', '수주잔고', 'AI 로봇']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>093240</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11110</v>
+        <v>14310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.72%</t>
+          <t>'+12.24%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="F5" t="n">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="G5" t="n">
-        <v>613</v>
+        <v>754</v>
       </c>
       <c r="H5" t="n">
-        <v>1.28</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,130 +871,130 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9770</v>
+        <v>12750</v>
       </c>
       <c r="K5" t="n">
-        <v>10320</v>
+        <v>13080</v>
       </c>
       <c r="L5" t="n">
-        <v>11690</v>
+        <v>14380</v>
       </c>
       <c r="M5" t="n">
-        <v>9690</v>
+        <v>12680</v>
       </c>
       <c r="N5" t="n">
-        <v>0.88</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>306035986030</v>
+        <v>149533985615</v>
       </c>
       <c r="P5" t="n">
-        <v>11690</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>2270</v>
+        <v>1640</v>
       </c>
       <c r="R5" t="n">
-        <v>-83000</v>
+        <v>87000</v>
       </c>
       <c r="S5" t="n">
-        <v>-114000</v>
+        <v>157000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 수주 잔고 1조원 돌파 및 삼성 관련 호재를 바탕으로 신고가 재돌파 기대감이 높으며, 9일 연속 상승세를 보이고 있습니다.</t>
+          <t>미국 AI 데이터센터향 광케이블 2차 물량 공급 개시 공시를 바탕으로 숏커버 및 2만원 이상 상승에 대한 기대감이 높습니다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['수주잔고', '로봇주', '신고가']</t>
+          <t>['광케이블', '공시', 'AI데이터센터']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>형지엘리트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14280</v>
+        <v>2140</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.00%</t>
+          <t>'+11.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>87</v>
+      </c>
+      <c r="F6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G6" t="n">
+        <v>226</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1924</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2310</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2090</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15852583543</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2665</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>292</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-105000</v>
+      </c>
+      <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>107</v>
-      </c>
-      <c r="F6" t="n">
-        <v>74</v>
-      </c>
-      <c r="G6" t="n">
-        <v>699</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>12750</v>
-      </c>
-      <c r="K6" t="n">
-        <v>13080</v>
-      </c>
-      <c r="L6" t="n">
-        <v>14380</v>
-      </c>
-      <c r="M6" t="n">
-        <v>12680</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O6" t="n">
-        <v>148117281305</v>
-      </c>
-      <c r="P6" t="n">
-        <v>31500</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1640</v>
-      </c>
-      <c r="R6" t="n">
-        <v>87000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>157000</v>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 AI 데이터센터향 광케이블 2차 물량 공급 개시 공시를 바탕으로 숏커버 및 2만원 이상 상승에 대한 기대감이 높습니다.</t>
+          <t>역대 최대 매출 및 3년 새 2배 성장 전망. 퀀텀 점프 기대감으로 상한가 및 연상 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광케이블', '공시', 'AI데이터센터']</t>
+          <t>['역대 최대 매출', '퀀텀 점프', '성장 전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>093240</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>푸드나무</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1296000</v>
+        <v>1610</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.97%</t>
+          <t>'+5.92%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>299</v>
       </c>
       <c r="F7" t="n">
-        <v>499</v>
+        <v>137</v>
       </c>
       <c r="G7" t="n">
-        <v>1576</v>
+        <v>586</v>
       </c>
       <c r="H7" t="n">
-        <v>48.77</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1223000</v>
+        <v>1520</v>
       </c>
       <c r="K7" t="n">
-        <v>1260000</v>
+        <v>1132</v>
       </c>
       <c r="L7" t="n">
-        <v>1329000</v>
+        <v>1952</v>
       </c>
       <c r="M7" t="n">
-        <v>1254000</v>
+        <v>1115</v>
       </c>
       <c r="N7" t="n">
-        <v>48.81</v>
+        <v>0.57</v>
       </c>
       <c r="O7" t="n">
-        <v>4754942329000</v>
+        <v>83087991601</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>3980</v>
       </c>
       <c r="Q7" t="n">
-        <v>468000</v>
+        <v>1115</v>
       </c>
       <c r="R7" t="n">
-        <v>430000</v>
+        <v>-184000</v>
       </c>
       <c r="S7" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>자사주 매입 완료 및 솔리다임 상장 관련 언급이 있으나, 전반적으로 이재명 정부와 최태원 회장에 대한 부정적 평가와 함께 주가 하락에 대한 불만이 표출되었습니다.</t>
+          <t>인수 관련 논의와 함께 주가 상승 및 하락 전망이 엇갈림. 공시 발표 및 주가 급등락에 대한 기대와 우려가 공존하며, 상장 폐지 가능성도 언급됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['솔리다임', '자사주', '주가']</t>
+          <t>['인수', '공시', '상장폐지']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>290720</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>푸드나무</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1601</v>
+        <v>1294000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.33%</t>
+          <t>'+5.81%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>290</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>133</v>
+        <v>503</v>
       </c>
       <c r="G8" t="n">
-        <v>543</v>
+        <v>1657</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6899999999999999</v>
+        <v>48.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1520</v>
+        <v>1223000</v>
       </c>
       <c r="K8" t="n">
-        <v>1132</v>
+        <v>1260000</v>
       </c>
       <c r="L8" t="n">
-        <v>1952</v>
+        <v>1329000</v>
       </c>
       <c r="M8" t="n">
-        <v>1115</v>
+        <v>1254000</v>
       </c>
       <c r="N8" t="n">
-        <v>0.57</v>
+        <v>48.81</v>
       </c>
       <c r="O8" t="n">
-        <v>82907724731</v>
+        <v>5134182673000</v>
       </c>
       <c r="P8" t="n">
-        <v>3980</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>1115</v>
+        <v>468000</v>
       </c>
       <c r="R8" t="n">
-        <v>-184000</v>
+        <v>430000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주당 3500원 인수 관련 언급과 함께 3연상 및 60% 상승에 대한 기대감이 있었으나, 상폐 및 거래정지 가능성도 제기되었습니다.</t>
+          <t>자사주 매입 종료와 함께 주가 변동성 발생. 솔리다임 관련 이슈 및 정치적 상황에 대한 부정적 언급이 있으나, 메모리 반도체 업황 개선 기대감도 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['인수', '공시', '상폐']</t>
+          <t>['자사주 매입', '메모리 반도체', '주주 친화책']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>290720</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>222500</v>
+        <v>223500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.20%</t>
+          <t>'+5.67%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="G9" t="n">
-        <v>1611</v>
+        <v>1594</v>
       </c>
       <c r="H9" t="n">
         <v>46.08</v>
@@ -1254,7 +1254,7 @@
         <v>46.04</v>
       </c>
       <c r="O9" t="n">
-        <v>3204583304750</v>
+        <v>3580677259250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 정부의 중국 반도체 퇴출 결정과 나스닥 선물 폭락 등 부정적 요인이 언급되었으나, 25만원 및 30만원 돌파 기대와 함께 100만원 황제주 가능성도 제기되었습니다.</t>
+          <t>미국 정부의 중국 반도체 제재 관련 뉴스와 함께 주가 상승 및 하락에 대한 상반된 전망이 혼재. 거시 경제 지표와 정치적 이슈가 주가에 영향을 미치는 것으로 보임.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '퇴출', '전망']</t>
+          <t>['반도체', '지정학적 리스크', '주가 전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14710</v>
+        <v>14770</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.88%</t>
+          <t>'+4.31%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F10" t="n">
         <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H10" t="n">
         <v>9.82</v>
@@ -1346,7 +1346,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>31985349175</v>
+        <v>32616545125</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2915</v>
+        <v>2905</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.64%</t>
+          <t>'+2.29%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
         <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H11" t="n">
         <v>5.82</v>
@@ -1438,7 +1438,7 @@
         <v>5.91</v>
       </c>
       <c r="O11" t="n">
-        <v>17732637409</v>
+        <v>17814802429</v>
       </c>
       <c r="P11" t="n">
         <v>19950</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17670</v>
+        <v>17680</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.02%</t>
+          <t>'+2.08%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.78</v>
       </c>
       <c r="O12" t="n">
-        <v>45304104130</v>
+        <v>48301288450</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1590,13 +1590,13 @@
         <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F13" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G13" t="n">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="H13" t="n">
         <v>22.23</v>
@@ -1622,7 +1622,7 @@
         <v>22.29</v>
       </c>
       <c r="O13" t="n">
-        <v>90956372350</v>
+        <v>98969627850</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1682,13 +1682,13 @@
         <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H14" t="n">
         <v>25.45</v>
@@ -1714,7 +1714,7 @@
         <v>25.4</v>
       </c>
       <c r="O14" t="n">
-        <v>15825518915</v>
+        <v>16932502415</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1774,13 +1774,13 @@
         <v>-0.93</v>
       </c>
       <c r="E15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F15" t="n">
         <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H15" t="n">
         <v>0.84</v>
@@ -1806,7 +1806,7 @@
         <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>33210054941</v>
+        <v>33343568841</v>
       </c>
       <c r="P15" t="n">
         <v>2970</v>
@@ -1866,13 +1866,13 @@
         <v>-0.73</v>
       </c>
       <c r="E16" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>11980563325</v>
+        <v>12129124345</v>
       </c>
       <c r="P16" t="n">
         <v>7050</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4305</v>
+        <v>4315</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.02%</t>
+          <t>'-6.80%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>73</v>
       </c>
       <c r="G17" t="n">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="H17" t="n">
         <v>8.58</v>
@@ -1990,7 +1990,7 @@
         <v>8.57</v>
       </c>
       <c r="O17" t="n">
-        <v>26089269291</v>
+        <v>26331440036</v>
       </c>
       <c r="P17" t="n">
         <v>7560</v>

--- a/data/trending_integrated_20261021_15.xlsx
+++ b/data/trending_integrated_20261021_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.27</v>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0.27</v>
       </c>
       <c r="O2" t="n">
-        <v>108874132020</v>
+        <v>108887494180</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.66</v>
       </c>
       <c r="E3" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="F3" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G3" t="n">
-        <v>600</v>
+        <v>624</v>
       </c>
       <c r="H3" t="n">
         <v>5.34</v>
@@ -702,7 +702,7 @@
         <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>67986492780</v>
+        <v>67988540970</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 상장 관련 이슈와 함께 주가 변동성 확대. 테슬라 관련 뉴스가 긍정적 영향을 미치나, 국내 주가 관리 및 거래량에 대한 불만이 제기됨.</t>
+          <t>명신산업의 국내 주가 관리 실패 및 미국 중복 상장 시도 실패 관련 내용과 함께, 테슬라 관련 호재 속 1만 원대 안착 전망 및 15,000원 돌파 기대감. 거래량 증가 및 VI 발동. 공매도 세력과의 공방.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['중복상장', '테슬라', '거래량']</t>
+          <t>['중복상장', '테슬라', '주가관리']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F4" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G4" t="n">
-        <v>640</v>
+        <v>668</v>
       </c>
       <c r="H4" t="n">
         <v>1.28</v>
@@ -794,7 +794,7 @@
         <v>0.88</v>
       </c>
       <c r="O4" t="n">
-        <v>307443591870</v>
+        <v>307578319030</v>
       </c>
       <c r="P4" t="n">
         <v>11690</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>데이터센터 수주 잔고 1조 원 이상 확보 소식과 함께 로봇 및 AI 섹터 전반의 강세. 삼성전자와의 연계 가능성이 부각되며 신고가 경신 기대감이 높음.</t>
+          <t>HT로보틱스의 인공지능 데이터센터 수주 잔고 1조원 돌파 및 삼성, ESS, 로봇, 이차전지 섹터 연관성에 따른 신고가 경신 기대감. 9일 연속 상승 및 투경 예고 속에서 고점 급락 가능성 경고. 시가총액 대비 높은 수주 잔고.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['데이터센터', '수주잔고', 'AI 로봇']</t>
+          <t>['수주잔고', '인공지능', '로봇']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>754</v>
+        <v>805</v>
       </c>
       <c r="H5" t="n">
         <v>3.15</v>
@@ -886,7 +886,7 @@
         <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>149533985615</v>
+        <v>149646075845</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -946,13 +946,13 @@
         <v>3.15</v>
       </c>
       <c r="E6" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H6" t="n">
         <v>3.94</v>
@@ -978,7 +978,7 @@
         <v>0.79</v>
       </c>
       <c r="O6" t="n">
-        <v>15852583543</v>
+        <v>15856833583</v>
       </c>
       <c r="P6" t="n">
         <v>2665</v>
@@ -1038,13 +1038,13 @@
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F7" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G7" t="n">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="H7" t="n">
         <v>0.6899999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>0.57</v>
       </c>
       <c r="O7" t="n">
-        <v>83087991601</v>
+        <v>83139843261</v>
       </c>
       <c r="P7" t="n">
         <v>3980</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>인수 관련 논의와 함께 주가 상승 및 하락 전망이 엇갈림. 공시 발표 및 주가 급등락에 대한 기대와 우려가 공존하며, 상장 폐지 가능성도 언급됨.</t>
+          <t>주당 3,500원 인수 관련 논란 및 상장 이래 최저가 기록 속에서, 3연상 및 1만원 목표 기대감과 함께 미친 매집 및 주포의 움직임 언급. 공시 내용에 따른 향방 주목. 투자자 간의 혼란과 희비 교차.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['인수', '공시', '상장폐지']</t>
+          <t>['인수', '공시', '매집']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G8" t="n">
-        <v>1657</v>
+        <v>1705</v>
       </c>
       <c r="H8" t="n">
         <v>48.77</v>
@@ -1162,7 +1162,7 @@
         <v>48.81</v>
       </c>
       <c r="O8" t="n">
-        <v>5134182673000</v>
+        <v>5135269633000</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 종료와 함께 주가 변동성 발생. 솔리다임 관련 이슈 및 정치적 상황에 대한 부정적 언급이 있으나, 메모리 반도체 업황 개선 기대감도 존재.</t>
+          <t>자사주 매입 종료 및 솔리다임 상장 관련 내용과 함께, 이재명 대통령 및 최태원 회장에 대한 부정적 언급이 다수. 일부에서는 메모리 호재에 따른 상승 기류 진입 및 주주 친화책 기대. 기관 대량 매수에도 불구하고 거짓 반등 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주 매입', '메모리 반도체', '주주 친화책']</t>
+          <t>['자사주매입', '솔리다임', '메모리']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1228,7 +1228,7 @@
         <v>519</v>
       </c>
       <c r="G9" t="n">
-        <v>1594</v>
+        <v>1627</v>
       </c>
       <c r="H9" t="n">
         <v>46.08</v>
@@ -1254,7 +1254,7 @@
         <v>46.04</v>
       </c>
       <c r="O9" t="n">
-        <v>3580677259250</v>
+        <v>3580751014250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 정부의 중국 반도체 제재 관련 뉴스와 함께 주가 상승 및 하락에 대한 상반된 전망이 혼재. 거시 경제 지표와 정치적 이슈가 주가에 영향을 미치는 것으로 보임.</t>
+          <t>미국 정부의 중국 반도체 퇴출 결정 속보와 더불어, 이재명 관련 부정적 언급과 함께 종가 음봉 마감을 보인 가운데, 일부에서는 100만원 황제주 전망 제시. 개인 투자자 간의 상반된 의견 대립.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '지정학적 리스크', '주가 전망']</t>
+          <t>['반도체', '퇴출', '전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="H10" t="n">
         <v>9.82</v>
@@ -1346,7 +1346,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>32616545125</v>
+        <v>32630222145</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>외국인 및 기관의 매수세 유입과 실적 우량주로서의 잠재력에 대한 긍정적 시각과 함께, 주가 조작 의혹 및 이재명 정부에 대한 비판이 존재합니다.</t>
+          <t>외국인 및 기관의 프로그램 매수세 유입 속에 실적 우량주로서의 대우건설에 대한 10만원 텐베거 가능성 언급. 주가 조작 의혹 및 이재명 대통령에 대한 비판적 시각 혼재. 연말 19,000원 목표 제시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['외인수급', '실적', '주가조작']</t>
+          <t>['실적', '매수세', '주가조작']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H11" t="n">
         <v>5.82</v>
@@ -1438,7 +1438,7 @@
         <v>5.91</v>
       </c>
       <c r="O11" t="n">
-        <v>17814802429</v>
+        <v>17816815594</v>
       </c>
       <c r="P11" t="n">
         <v>19950</v>
@@ -1498,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F12" t="n">
         <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="H12" t="n">
         <v>27.78</v>
@@ -1530,7 +1530,7 @@
         <v>27.78</v>
       </c>
       <c r="O12" t="n">
-        <v>48301288450</v>
+        <v>48303233250</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1590,13 +1590,13 @@
         <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F13" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G13" t="n">
-        <v>680</v>
+        <v>654</v>
       </c>
       <c r="H13" t="n">
         <v>22.23</v>
@@ -1622,7 +1622,7 @@
         <v>22.29</v>
       </c>
       <c r="O13" t="n">
-        <v>98969627850</v>
+        <v>99043668850</v>
       </c>
       <c r="P13" t="n">
         <v>139200</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>야간 선물 폭등과 반도체 및 원전/전력 섹터 상승 기대감이 있으나, 주가 누르기 및 하락에 대한 불만과 함께 외인 매도에 따른 박살 가능성이 언급되었습니다.</t>
+          <t>원전주 약세 속에서 두산에너빌리티의 주가 누르기 방지법 청원 동참 요구. 연기금 매도 및 지수 하락 대비 현저히 낮은 상승률에 대한 불만 표출. 개미 투자자들의 인내와 버팀 요구. 대책 없는 정부 및 관련 정책 비판.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '전력', '주가']</t>
+          <t>['원전주', '주가누르기', '정책']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="H14" t="n">
         <v>25.45</v>
@@ -1714,7 +1714,7 @@
         <v>25.4</v>
       </c>
       <c r="O14" t="n">
-        <v>16932502415</v>
+        <v>16933237415</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1806,7 +1806,7 @@
         <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>33343568841</v>
+        <v>33343990441</v>
       </c>
       <c r="P15" t="n">
         <v>2970</v>
@@ -1898,7 +1898,7 @@
         <v>0.73</v>
       </c>
       <c r="O16" t="n">
-        <v>12129124345</v>
+        <v>12135610255</v>
       </c>
       <c r="P16" t="n">
         <v>7050</v>
@@ -1961,10 +1961,10 @@
         <v>111</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G17" t="n">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="H17" t="n">
         <v>8.58</v>
@@ -1990,7 +1990,7 @@
         <v>8.57</v>
       </c>
       <c r="O17" t="n">
-        <v>26331440036</v>
+        <v>26341485356</v>
       </c>
       <c r="P17" t="n">
         <v>7560</v>
